--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:17:51+00:00</t>
+    <t>2023-02-15T16:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:22:21+00:00</t>
+    <t>2023-02-15T20:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T20:04:03+00:00</t>
+    <t>2023-02-16T23:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-16T23:28:10+00:00</t>
+    <t>2023-02-17T19:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-17T19:45:07+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
+++ b/refs/heads/master/StructureDefinition-ExtBoolPertinenciaAtencionBox.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
